--- a/astro-site/public/dl/taco-shop-business-plan/taco-shop-financial-projections.xlsx
+++ b/astro-site/public/dl/taco-shop-business-plan/taco-shop-financial-projections.xlsx
@@ -826,7 +826,7 @@
         <v>18.900000000000002</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, menu prices include VAT.","")</f>
+        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, "&amp;"menu prices include VAT.","")</f>
         <v>Average check excl. sales tax plus the weighted sales tax of your sales lines (8%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, menu prices include VAT.</v>
       </c>
     </row>

--- a/astro-site/public/dl/taco-shop-business-plan/taco-shop-financial-projections.xlsx
+++ b/astro-site/public/dl/taco-shop-business-plan/taco-shop-financial-projections.xlsx
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>
@@ -8968,7 +8968,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="29" t="n"/>

--- a/astro-site/public/dl/taco-shop-business-plan/taco-shop-financial-projections.xlsx
+++ b/astro-site/public/dl/taco-shop-business-plan/taco-shop-financial-projections.xlsx
@@ -826,7 +826,7 @@
         <v>18.900000000000002</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, menu prices include VAT.","")</f>
+        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, "&amp;"menu prices include VAT.","")</f>
         <v>Average check excl. sales tax plus the weighted sales tax of your sales lines (8%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, menu prices include VAT.</v>
       </c>
     </row>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>How far you can fall below plan before you start losing money</t>
+          <t>How far planned sales must sit above cash break-even (fixed costs and the loan payment). The drop you can absorb is somewhat smaller: with a 15% cushion, about 13% of plan</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>How far you can fall before you cannot pay the fixed costs and the loan payment. The required minimum is set in the "0. Assumptions" tab</t>
+          <t>How far planned sales sit above cash break-even. The drop you can absorb before you cannot pay the fixed costs and the loan payment is somewhat smaller: with a 25% cushion, 20%. The required minimum is set in the "0. Assumptions" tab</t>
         </is>
       </c>
       <c r="F24" s="29" t="n"/>
@@ -8968,7 +8968,7 @@
     <row r="34" ht="134.75" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
         <is>
-          <t>Fourth-quarter sales tax is settled in January of the following year, so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
+          <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
         </is>
       </c>
       <c r="B34" s="29" t="n"/>

--- a/astro-site/public/dl/taco-shop-business-plan/taco-shop-financial-projections.xlsx
+++ b/astro-site/public/dl/taco-shop-business-plan/taco-shop-financial-projections.xlsx
@@ -8965,7 +8965,7 @@
       <c r="N33" s="29" t="n"/>
       <c r="O33" s="29" t="n"/>
     </row>
-    <row r="34" ht="134.75" customHeight="1">
+    <row r="34" ht="149.5" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
         <is>
           <t>Fourth-quarter sales tax is settled in Month 13 (January of the following year when Month 1 is January), so it does not appear in this table. The model pays year-1 income tax in July of year 2 (a simplification: estimated tax payments are usually quarterly). The loan payment is spread in twelve equal parts following the ANNUAL schedule in the Financing tab, and payroll in twelve monthly installments (plus extra pay periods in their month, only if pay periods &gt; 12).</t>
